--- a/MCU_pins.xlsx
+++ b/MCU_pins.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antoi\Documents\Github\Trotten-Electric-Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B15D15E-577B-4A3C-9B91-2FEFC77F2B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4C9555-CC64-4B2B-8638-5455257EE613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="3270" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="i2C addresses" sheetId="1" r:id="rId1"/>
     <sheet name="Interrupt pins" sheetId="2" r:id="rId2"/>
+    <sheet name="motor pins" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Device</t>
   </si>
@@ -50,6 +51,24 @@
   </si>
   <si>
     <t>0x40</t>
+  </si>
+  <si>
+    <t>PIN</t>
+  </si>
+  <si>
+    <t>Motor func</t>
+  </si>
+  <si>
+    <t>R_EN</t>
+  </si>
+  <si>
+    <t>R_PWM</t>
+  </si>
+  <si>
+    <t>L_EN</t>
+  </si>
+  <si>
+    <t>L_PWM</t>
   </si>
 </sst>
 </file>
@@ -368,7 +387,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
     <col min="2" max="2" width="12.140625" customWidth="1"/>
@@ -415,8 +434,58 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB06BBBC-09FA-4BF9-87AC-BCCD6E34B555}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{352EB838-9922-4952-BBCB-847999B79ADF}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>